--- a/data/Mörel-Filet/investment_decision/Filet_SFH_from_2015_investment_decision.xlsx
+++ b/data/Mörel-Filet/investment_decision/Filet_SFH_from_2015_investment_decision.xlsx
@@ -569,7 +569,7 @@
         <v>49675</v>
       </c>
       <c r="B4" t="n">
-        <v>15.66760527221639</v>
+        <v>9.25496678421495</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -583,19 +583,19 @@
         <v>2809.813757328734</v>
       </c>
       <c r="F4" t="n">
-        <v>15.61824254992701</v>
+        <v>9.251636094928722</v>
       </c>
       <c r="G4" t="n">
         <v>2809.813757328734</v>
       </c>
       <c r="H4" t="n">
-        <v>15.61824254992701</v>
+        <v>9.215054635046293</v>
       </c>
       <c r="I4" t="n">
         <v>2809.813757328734</v>
       </c>
       <c r="J4" t="n">
-        <v>15.66760527221639</v>
+        <v>9.245493157804416</v>
       </c>
       <c r="K4" t="n">
         <v>2809.813757328734</v>
@@ -606,7 +606,7 @@
         <v>51502</v>
       </c>
       <c r="B5" t="n">
-        <v>15.66760527221639</v>
+        <v>9.25496678421495</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -620,19 +620,19 @@
         <v>2809.813757328734</v>
       </c>
       <c r="F5" t="n">
-        <v>15.61824254992701</v>
+        <v>9.251636094928722</v>
       </c>
       <c r="G5" t="n">
         <v>2809.813757328734</v>
       </c>
       <c r="H5" t="n">
-        <v>15.61824254992701</v>
+        <v>9.215054635046293</v>
       </c>
       <c r="I5" t="n">
         <v>2809.813757328734</v>
       </c>
       <c r="J5" t="n">
-        <v>15.66760527221639</v>
+        <v>9.245493157804416</v>
       </c>
       <c r="K5" t="n">
         <v>2809.813757328734</v>
@@ -643,7 +643,7 @@
         <v>53328</v>
       </c>
       <c r="B6" t="n">
-        <v>15.67039133598036</v>
+        <v>10.22620162385679</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -657,19 +657,19 @@
         <v>2809.813757328734</v>
       </c>
       <c r="F6" t="n">
-        <v>15.67039133598036</v>
+        <v>10.22643570092313</v>
       </c>
       <c r="G6" t="n">
         <v>2809.813757328734</v>
       </c>
       <c r="H6" t="n">
-        <v>15.67039133598036</v>
+        <v>10.21686594440428</v>
       </c>
       <c r="I6" t="n">
         <v>2809.813757328734</v>
       </c>
       <c r="J6" t="n">
-        <v>15.67039133598036</v>
+        <v>10.22279655156232</v>
       </c>
       <c r="K6" t="n">
         <v>2809.813757328734</v>
@@ -684,32 +684,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Filet_b_SFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Filet_b_SFH_from_2015</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E7" t="n">
-        <v>4.214720635993101</v>
+        <v>6.316318651685394</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>4.214720635993101</v>
+        <v>6.316318651685394</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>4.214720635993101</v>
+        <v>6.316318651685394</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>4.214720635993101</v>
+        <v>6.316318651685394</v>
       </c>
     </row>
     <row r="8">
@@ -721,32 +721,32 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Filet_b_SFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Filet_b_SFH_from_2015</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E8" t="n">
-        <v>4.214720635993101</v>
+        <v>6.316318651685394</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>4.214720635993101</v>
+        <v>6.316318651685394</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>4.214720635993101</v>
+        <v>6.316318651685394</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>4.214720635993101</v>
+        <v>6.316318651685394</v>
       </c>
     </row>
     <row r="9">
@@ -758,32 +758,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Filet_b_SFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Filet_b_SFH_from_2015</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E9" t="n">
-        <v>4.214720635993101</v>
+        <v>6.316318651685394</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>4.214720635993101</v>
+        <v>6.316318651685394</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>4.214720635993101</v>
+        <v>6.316318651685394</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>4.214720635993101</v>
+        <v>6.316318651685394</v>
       </c>
     </row>
     <row r="10">
@@ -795,32 +795,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Filet_b_SFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Filet_b_SFH_from_2015</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E10" t="n">
-        <v>4.214720635993101</v>
+        <v>6.316318651685394</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>4.214720635993101</v>
+        <v>6.316318651685394</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>4.214720635993101</v>
+        <v>6.316318651685394</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>4.214720635993101</v>
+        <v>6.316318651685394</v>
       </c>
     </row>
     <row r="11">
@@ -832,32 +832,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Filet_b_SFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Filet_b_SFH_from_2015</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E11" t="n">
-        <v>4.214720635993101</v>
+        <v>6.316318651685394</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>4.214720635993101</v>
+        <v>6.316318651685394</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>4.214720635993101</v>
+        <v>6.316318651685394</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>4.214720635993101</v>
+        <v>6.316318651685394</v>
       </c>
     </row>
     <row r="12">
@@ -865,7 +865,7 @@
         <v>46023</v>
       </c>
       <c r="B12" t="n">
-        <v>0.001082218447058824</v>
+        <v>0.0007575529129411767</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -879,19 +879,19 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.001082218447058824</v>
+        <v>0.0007575529129411767</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.001082218447058824</v>
+        <v>0.0007575529129411767</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0.001082218447058824</v>
+        <v>0.0007575529129411767</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
@@ -902,7 +902,7 @@
         <v>47849</v>
       </c>
       <c r="B13" t="n">
-        <v>0.001082218447058824</v>
+        <v>0.0007575529129411767</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -916,19 +916,19 @@
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0.001082218447058824</v>
+        <v>0.0007575529129411767</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.001082218447058824</v>
+        <v>0.0007575529129411767</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0.001082218447058824</v>
+        <v>0.0007575529129411767</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -939,7 +939,7 @@
         <v>49675</v>
       </c>
       <c r="B14" t="n">
-        <v>0.001244551214117647</v>
+        <v>0.001136329369411765</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -953,19 +953,19 @@
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0.001244551214117647</v>
+        <v>0.001136329369411765</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.001292169731849013</v>
+        <v>0.001136329369411765</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0.001244551214117647</v>
+        <v>0.001136329369411765</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
@@ -976,7 +976,7 @@
         <v>51502</v>
       </c>
       <c r="B15" t="n">
-        <v>0.001244551214117641</v>
+        <v>0.001136329369411765</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -990,19 +990,19 @@
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0.001251127618571832</v>
+        <v>0.001136329369411765</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.001298662136470588</v>
+        <v>0.001136329369411765</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.001244551214117647</v>
+        <v>0.001136329369411765</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -1013,7 +1013,7 @@
         <v>53328</v>
       </c>
       <c r="B16" t="n">
-        <v>0.001286171627160314</v>
+        <v>0.001136329369411765</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1027,19 +1027,19 @@
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0.001298662136470588</v>
+        <v>0.001136329369411765</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.001298662136470588</v>
+        <v>0.001136329369411765</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.001298662136470588</v>
+        <v>0.001136329369411765</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
@@ -1124,7 +1124,7 @@
         <v>49675</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6323057927477076</v>
+        <v>0.4007027975714724</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1138,19 +1138,19 @@
         <v>0.9658799640000001</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6323057927477074</v>
+        <v>0.4007027975714724</v>
       </c>
       <c r="G19" t="n">
         <v>0.9658799640000001</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6323057927477074</v>
+        <v>0.3983401846339659</v>
       </c>
       <c r="I19" t="n">
         <v>0.9658799640000001</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6323057927477076</v>
+        <v>0.3988649510770472</v>
       </c>
       <c r="K19" t="n">
         <v>0.9658799640000001</v>
@@ -1161,7 +1161,7 @@
         <v>51502</v>
       </c>
       <c r="B20" t="n">
-        <v>0.632421405</v>
+        <v>0.4007027975714724</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1175,19 +1175,19 @@
         <v>0.9658799640000001</v>
       </c>
       <c r="F20" t="n">
-        <v>0.632421405</v>
+        <v>0.4007027975714724</v>
       </c>
       <c r="G20" t="n">
         <v>0.9658799640000001</v>
       </c>
       <c r="H20" t="n">
-        <v>0.632421405</v>
+        <v>0.3983401846339659</v>
       </c>
       <c r="I20" t="n">
         <v>0.9658799640000001</v>
       </c>
       <c r="J20" t="n">
-        <v>0.632421405</v>
+        <v>0.3988649510770472</v>
       </c>
       <c r="K20" t="n">
         <v>0.9658799640000001</v>
@@ -1198,7 +1198,7 @@
         <v>53328</v>
       </c>
       <c r="B21" t="n">
-        <v>0.632421405</v>
+        <v>0.4007027975714724</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1212,19 +1212,19 @@
         <v>0.9658799640000001</v>
       </c>
       <c r="F21" t="n">
-        <v>0.632421405</v>
+        <v>0.4007027975714724</v>
       </c>
       <c r="G21" t="n">
         <v>0.9658799640000001</v>
       </c>
       <c r="H21" t="n">
-        <v>0.632421405</v>
+        <v>0.3983401846339659</v>
       </c>
       <c r="I21" t="n">
         <v>0.9658799640000001</v>
       </c>
       <c r="J21" t="n">
-        <v>0.632421405</v>
+        <v>0.3988649510770472</v>
       </c>
       <c r="K21" t="n">
         <v>0.9658799640000001</v>
@@ -1494,7 +1494,7 @@
         <v>49675</v>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>0.2587178475</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1508,19 +1508,19 @@
         <v>0.9658799640000001</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>0.2587178475</v>
       </c>
       <c r="G29" t="n">
         <v>0.9658799640000001</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>0.2610804604375064</v>
       </c>
       <c r="I29" t="n">
         <v>0.9658799640000001</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>0.2605556939944252</v>
       </c>
       <c r="K29" t="n">
         <v>0.9658799640000001</v>
@@ -1531,7 +1531,7 @@
         <v>51502</v>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>0.2587178475</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1545,19 +1545,19 @@
         <v>0.9658799640000001</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>0.2587178475</v>
       </c>
       <c r="G30" t="n">
         <v>0.9658799640000001</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>0.2610804604375064</v>
       </c>
       <c r="I30" t="n">
         <v>0.9658799640000001</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.2605556939944252</v>
       </c>
       <c r="K30" t="n">
         <v>0.9658799640000001</v>
@@ -1568,7 +1568,7 @@
         <v>53328</v>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>0.2587178475</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1582,19 +1582,19 @@
         <v>0.9658799640000001</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>0.2587178475</v>
       </c>
       <c r="G31" t="n">
         <v>0.9658799640000001</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>0.2610804604375064</v>
       </c>
       <c r="I31" t="n">
         <v>0.9658799640000001</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>0.2605556939944252</v>
       </c>
       <c r="K31" t="n">
         <v>0.9658799640000001</v>
@@ -2419,7 +2419,7 @@
         <v>49675</v>
       </c>
       <c r="B54" t="n">
-        <v>1.412696235970087</v>
+        <v>1.421361671219424</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2433,19 +2433,19 @@
         <v>5.354298805529662</v>
       </c>
       <c r="F54" t="n">
-        <v>1.332541959018701</v>
+        <v>1.313661283367636</v>
       </c>
       <c r="G54" t="n">
         <v>5.354298805529662</v>
       </c>
       <c r="H54" t="n">
-        <v>1.331132540081814</v>
+        <v>1.313696609113538</v>
       </c>
       <c r="I54" t="n">
         <v>5.354298805529662</v>
       </c>
       <c r="J54" t="n">
-        <v>1.412696235970087</v>
+        <v>1.421533972862481</v>
       </c>
       <c r="K54" t="n">
         <v>5.354298805529662</v>
@@ -2456,7 +2456,7 @@
         <v>51502</v>
       </c>
       <c r="B55" t="n">
-        <v>1.412696235970087</v>
+        <v>1.421361671219424</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2470,19 +2470,19 @@
         <v>5.354298805529662</v>
       </c>
       <c r="F55" t="n">
-        <v>1.332541959018701</v>
+        <v>1.313661283367636</v>
       </c>
       <c r="G55" t="n">
         <v>5.354298805529662</v>
       </c>
       <c r="H55" t="n">
-        <v>1.331132540081814</v>
+        <v>1.313696609113538</v>
       </c>
       <c r="I55" t="n">
         <v>5.354298805529662</v>
       </c>
       <c r="J55" t="n">
-        <v>1.412696235970087</v>
+        <v>1.421533972862481</v>
       </c>
       <c r="K55" t="n">
         <v>5.354298805529662</v>
@@ -2493,7 +2493,7 @@
         <v>53328</v>
       </c>
       <c r="B56" t="n">
-        <v>1.412696235970087</v>
+        <v>1.421361671219424</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2507,19 +2507,19 @@
         <v>5.354298805529662</v>
       </c>
       <c r="F56" t="n">
-        <v>1.332541959018701</v>
+        <v>1.313661283367636</v>
       </c>
       <c r="G56" t="n">
         <v>5.354298805529662</v>
       </c>
       <c r="H56" t="n">
-        <v>1.331132540081814</v>
+        <v>1.313696609113538</v>
       </c>
       <c r="I56" t="n">
         <v>5.354298805529662</v>
       </c>
       <c r="J56" t="n">
-        <v>1.412696235970087</v>
+        <v>1.421533972862481</v>
       </c>
       <c r="K56" t="n">
         <v>5.354298805529662</v>
@@ -2789,7 +2789,7 @@
         <v>49675</v>
       </c>
       <c r="B64" t="n">
-        <v>0.7040325891623208</v>
+        <v>0.3708735732301736</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2803,19 +2803,19 @@
         <v>5.354298805529662</v>
       </c>
       <c r="F64" t="n">
-        <v>0.7852757496936196</v>
+        <v>0.4786527846516579</v>
       </c>
       <c r="G64" t="n">
         <v>5.354298805529662</v>
       </c>
       <c r="H64" t="n">
-        <v>0.7866851686305072</v>
+        <v>0.4794831899916777</v>
       </c>
       <c r="I64" t="n">
         <v>5.354298805529662</v>
       </c>
       <c r="J64" t="n">
-        <v>0.7040325891623213</v>
+        <v>0.3709254729422937</v>
       </c>
       <c r="K64" t="n">
         <v>5.354298805529662</v>
@@ -2826,7 +2826,7 @@
         <v>51502</v>
       </c>
       <c r="B65" t="n">
-        <v>0.7040325891623208</v>
+        <v>0.3747029444830872</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -2840,19 +2840,19 @@
         <v>5.354298805529662</v>
       </c>
       <c r="F65" t="n">
-        <v>0.7852757496936196</v>
+        <v>0.4824191994808961</v>
       </c>
       <c r="G65" t="n">
         <v>5.354298805529662</v>
       </c>
       <c r="H65" t="n">
-        <v>0.7866851686305072</v>
+        <v>0.4832917914914554</v>
       </c>
       <c r="I65" t="n">
         <v>5.354298805529662</v>
       </c>
       <c r="J65" t="n">
-        <v>0.7040325891623213</v>
+        <v>0.374801115771877</v>
       </c>
       <c r="K65" t="n">
         <v>5.354298805529662</v>
@@ -2863,7 +2863,7 @@
         <v>53328</v>
       </c>
       <c r="B66" t="n">
-        <v>1.05843644633876</v>
+        <v>0.6056454379348629</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -2877,19 +2877,19 @@
         <v>5.354298805529662</v>
       </c>
       <c r="F66" t="n">
-        <v>1.138590723290146</v>
+        <v>0.7133379040180846</v>
       </c>
       <c r="G66" t="n">
         <v>5.354298805529662</v>
       </c>
       <c r="H66" t="n">
-        <v>1.140000142227033</v>
+        <v>0.7136264433887709</v>
       </c>
       <c r="I66" t="n">
         <v>5.354298805529662</v>
       </c>
       <c r="J66" t="n">
-        <v>1.05843644633876</v>
+        <v>0.6055883726756643</v>
       </c>
       <c r="K66" t="n">
         <v>5.354298805529662</v>
